--- a/output_image/典型日1_09-16_逐时数据.xlsx
+++ b/output_image/典型日1_09-16_逐时数据.xlsx
@@ -1757,13 +1757,13 @@
         <v>0</v>
       </c>
       <c r="R9">
-        <v>84.55708026885986</v>
+        <v>61.43283653259277</v>
       </c>
       <c r="S9">
         <v>0.03479080647230148</v>
       </c>
       <c r="T9">
-        <v>84.52228946238756</v>
+        <v>61.39804572612047</v>
       </c>
       <c r="U9">
         <v>0.4125</v>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>11.73708057403564</v>
+        <v>-11.38716316223145</v>
       </c>
       <c r="Y9">
         <v>89.17846493721008</v>
@@ -1873,13 +1873,13 @@
         <v>0</v>
       </c>
       <c r="R10">
-        <v>76.09708118438721</v>
+        <v>52.97283744812012</v>
       </c>
       <c r="S10">
         <v>0.03539048880338669</v>
       </c>
       <c r="T10">
-        <v>76.06169069558382</v>
+        <v>52.93744695931673</v>
       </c>
       <c r="U10">
         <v>0.4125</v>
@@ -1891,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>11.73708057403564</v>
+        <v>-11.38716316223145</v>
       </c>
       <c r="Y10">
         <v>80.71846585273742</v>
@@ -1989,13 +1989,13 @@
         <v>0</v>
       </c>
       <c r="R11">
-        <v>70.45708185976201</v>
+        <v>52.01103706359864</v>
       </c>
       <c r="S11">
         <v>0.03776615858078003</v>
       </c>
       <c r="T11">
-        <v>70.41931570118123</v>
+        <v>51.97327090501786</v>
       </c>
       <c r="U11">
         <v>0.4125</v>
@@ -2007,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>11.7370806390589</v>
+        <v>-6.708964157104492</v>
       </c>
       <c r="Y11">
         <v>84.07846649966457</v>
@@ -2105,13 +2105,13 @@
         <v>0</v>
       </c>
       <c r="R12">
-        <v>73.69707977614806</v>
+        <v>59.02118927001953</v>
       </c>
       <c r="S12">
         <v>0.03751333430409431</v>
       </c>
       <c r="T12">
-        <v>73.65956644184396</v>
+        <v>58.98367593571544</v>
       </c>
       <c r="U12">
         <v>0.4125</v>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>11.73708069167541</v>
+        <v>-2.938809814453125</v>
       </c>
       <c r="Y12">
         <v>87.3184643911811</v>
@@ -2221,13 +2221,13 @@
         <v>0</v>
       </c>
       <c r="R13">
-        <v>65.65707890320338</v>
+        <v>54.02554859924317</v>
       </c>
       <c r="S13">
         <v>0.03724806383252144</v>
       </c>
       <c r="T13">
-        <v>65.61983083937086</v>
+        <v>53.98830053541064</v>
       </c>
       <c r="U13">
         <v>0.4125</v>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>11.73708073425808</v>
+        <v>0.1055504302978516</v>
       </c>
       <c r="Y13">
         <v>70.27846347565375</v>
@@ -2337,13 +2337,13 @@
         <v>0</v>
       </c>
       <c r="R14">
-        <v>66.1070834808401</v>
+        <v>54.47555317687988</v>
       </c>
       <c r="S14">
         <v>0.03538668900728226</v>
       </c>
       <c r="T14">
-        <v>66.07169679183282</v>
+        <v>54.4401664878726</v>
       </c>
       <c r="U14">
         <v>0.4125</v>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>11.73708073425808</v>
+        <v>0.1055504302978516</v>
       </c>
       <c r="Y14">
         <v>70.72846807459035</v>
@@ -2453,13 +2453,13 @@
         <v>0</v>
       </c>
       <c r="R15">
-        <v>56.89708058167018</v>
+        <v>45.26555027770996</v>
       </c>
       <c r="S15">
         <v>0.0363473929464817</v>
       </c>
       <c r="T15">
-        <v>56.8607331887237</v>
+        <v>45.22920288476347</v>
       </c>
       <c r="U15">
         <v>0.4125</v>
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>11.73708073425808</v>
+        <v>0.1055504302978516</v>
       </c>
       <c r="Y15">
         <v>61.51846519158553</v>
@@ -2569,13 +2569,13 @@
         <v>0</v>
       </c>
       <c r="R16">
-        <v>67.36707798767604</v>
+        <v>55.73554768371582</v>
       </c>
       <c r="S16">
         <v>0.03616251423954964</v>
       </c>
       <c r="T16">
-        <v>67.33091547343649</v>
+        <v>55.69938516947627</v>
       </c>
       <c r="U16">
         <v>0.4125</v>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>11.73708073425808</v>
+        <v>0.1055504302978516</v>
       </c>
       <c r="Y16">
         <v>71.98846260986129</v>
@@ -2685,13 +2685,13 @@
         <v>0</v>
       </c>
       <c r="R17">
-        <v>60.07708088684596</v>
+        <v>48.44555058288574</v>
       </c>
       <c r="S17">
         <v>0.03669863194227219</v>
       </c>
       <c r="T17">
-        <v>60.04038225490369</v>
+        <v>48.40885195094346</v>
       </c>
       <c r="U17">
         <v>0.525</v>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>11.73708073425808</v>
+        <v>0.1055504302978516</v>
       </c>
       <c r="Y17">
         <v>73.69846551834586</v>
@@ -2801,13 +2801,13 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <v>62.74708287048854</v>
+        <v>51.11555256652832</v>
       </c>
       <c r="S18">
         <v>0.03584675490856171</v>
       </c>
       <c r="T18">
-        <v>62.71123611557998</v>
+        <v>51.07970581161975</v>
       </c>
       <c r="U18">
         <v>0.525</v>
@@ -2819,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="X18">
-        <v>11.73708073425808</v>
+        <v>0.1055504302978516</v>
       </c>
       <c r="Y18">
         <v>76.36846750906066</v>
@@ -2917,13 +2917,13 @@
         <v>0</v>
       </c>
       <c r="R19">
-        <v>65.86707798767604</v>
+        <v>54.23554768371582</v>
       </c>
       <c r="S19">
         <v>0.03683951497077942</v>
       </c>
       <c r="T19">
-        <v>65.83023847270526</v>
+        <v>54.19870816874504</v>
       </c>
       <c r="U19">
         <v>0.525</v>
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="X19">
-        <v>11.73708073425808</v>
+        <v>0.1055504302978516</v>
       </c>
       <c r="Y19">
         <v>79.48846262624816</v>
@@ -3033,13 +3033,13 @@
         <v>0</v>
       </c>
       <c r="R20">
-        <v>49.27708164978542</v>
+        <v>37.64555134582519</v>
       </c>
       <c r="S20">
         <v>0.03561307117342949</v>
       </c>
       <c r="T20">
-        <v>49.24146857861199</v>
+        <v>37.60993827465176</v>
       </c>
       <c r="U20">
         <v>0.525</v>
@@ -3051,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="X20">
-        <v>11.73708073425808</v>
+        <v>0.1055504302978516</v>
       </c>
       <c r="Y20">
         <v>62.89846628835754</v>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="R21">
-        <v>49.48708073425807</v>
+        <v>37.85555043029785</v>
       </c>
       <c r="S21">
         <v>0.03604799881577492</v>
       </c>
       <c r="T21">
-        <v>49.4510327354423</v>
+        <v>37.81950243148207</v>
       </c>
       <c r="U21">
         <v>0.525</v>
@@ -3167,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="X21">
-        <v>11.73708073425808</v>
+        <v>0.1055504302978516</v>
       </c>
       <c r="Y21">
         <v>54.1084653728302</v>
@@ -3265,13 +3265,13 @@
         <v>0</v>
       </c>
       <c r="R22">
-        <v>55.90707890320338</v>
+        <v>44.27554859924316</v>
       </c>
       <c r="S22">
         <v>0.04384546354413033</v>
       </c>
       <c r="T22">
-        <v>55.86323343965925</v>
+        <v>44.23170313569903</v>
       </c>
       <c r="U22">
         <v>0.525</v>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="X22">
-        <v>11.73708073425808</v>
+        <v>0.1055504302978516</v>
       </c>
       <c r="Y22">
         <v>60.52846354177551</v>
@@ -3381,13 +3381,13 @@
         <v>0</v>
       </c>
       <c r="R23">
-        <v>62.80708046763081</v>
+        <v>53.93149734424792</v>
       </c>
       <c r="S23">
         <v>0.06628420203924179</v>
       </c>
       <c r="T23">
-        <v>62.74079626559157</v>
+        <v>53.86521314220867</v>
       </c>
       <c r="U23">
         <v>0.525</v>
@@ -3399,7 +3399,7 @@
         <v>0</v>
       </c>
       <c r="X23">
-        <v>11.7370807728066</v>
+        <v>2.8614976494237</v>
       </c>
       <c r="Y23">
         <v>67.42846506765441</v>
@@ -3497,13 +3497,13 @@
         <v>0</v>
       </c>
       <c r="R24">
-        <v>57.70708199350972</v>
+        <v>48.83149887012682</v>
       </c>
       <c r="S24">
         <v>0.8188387751579285</v>
       </c>
       <c r="T24">
-        <v>56.88824321835179</v>
+        <v>48.01266009496889</v>
       </c>
       <c r="U24">
         <v>0.525</v>
@@ -3515,7 +3515,7 @@
         <v>0</v>
       </c>
       <c r="X24">
-        <v>11.7370807728066</v>
+        <v>2.8614976494237</v>
       </c>
       <c r="Y24">
         <v>62.32846659353332</v>
@@ -3613,13 +3613,13 @@
         <v>0</v>
       </c>
       <c r="R25">
-        <v>56.71708031504292</v>
+        <v>47.84149719166003</v>
       </c>
       <c r="S25">
         <v>2.338675975799561</v>
       </c>
       <c r="T25">
-        <v>54.37840433924336</v>
+        <v>45.50282121586046</v>
       </c>
       <c r="U25">
         <v>0.525</v>
@@ -3631,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="X25">
-        <v>11.7370807728066</v>
+        <v>2.8614976494237</v>
       </c>
       <c r="Y25">
         <v>61.33846491506652</v>
@@ -3729,13 +3729,13 @@
         <v>0</v>
       </c>
       <c r="R26">
-        <v>58.57708095750065</v>
+        <v>51.99686206122873</v>
       </c>
       <c r="S26">
         <v>2.488569736480713</v>
       </c>
       <c r="T26">
-        <v>56.08851122101994</v>
+        <v>49.50829232474802</v>
       </c>
       <c r="U26">
         <v>0.525</v>
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="X26">
-        <v>11.73708080491276</v>
+        <v>5.156861908640844</v>
       </c>
       <c r="Y26">
         <v>63.19846552541809</v>
@@ -3845,13 +3845,13 @@
         <v>0</v>
       </c>
       <c r="R27">
-        <v>71.31708266200911</v>
+        <v>66.59865919439389</v>
       </c>
       <c r="S27">
         <v>3.483728885650635</v>
       </c>
       <c r="T27">
-        <v>67.83335377635848</v>
+        <v>63.11493030874325</v>
       </c>
       <c r="U27">
         <v>0.525</v>
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="X27">
-        <v>11.73708083095443</v>
+        <v>7.018657363339195</v>
       </c>
       <c r="Y27">
         <v>61.93846720388488</v>
@@ -3961,13 +3961,13 @@
         <v>0</v>
       </c>
       <c r="R28">
-        <v>84.87708022060286</v>
+        <v>80.15865675298764</v>
       </c>
       <c r="S28">
         <v>7.872257232666016</v>
       </c>
       <c r="T28">
-        <v>77.00482298793685</v>
+        <v>72.28639952032162</v>
       </c>
       <c r="U28">
         <v>0.525</v>
@@ -3979,7 +3979,7 @@
         <v>0.5744514465332031</v>
       </c>
       <c r="X28">
-        <v>11.73708083095443</v>
+        <v>7.018657363339195</v>
       </c>
       <c r="Y28">
         <v>75.49846476247863</v>
@@ -4077,13 +4077,13 @@
         <v>0</v>
       </c>
       <c r="R29">
-        <v>88.53708390414081</v>
+        <v>80.32559731553708</v>
       </c>
       <c r="S29">
         <v>14.4836368560791</v>
       </c>
       <c r="T29">
-        <v>74.05344704806171</v>
+        <v>65.84196045945798</v>
       </c>
       <c r="U29">
         <v>0.525</v>
@@ -4095,7 +4095,7 @@
         <v>1</v>
       </c>
       <c r="X29">
-        <v>11.737080852383</v>
+        <v>3.525594263779267</v>
       </c>
       <c r="Y29">
         <v>88.15846842458801</v>
@@ -4193,13 +4193,13 @@
         <v>0</v>
       </c>
       <c r="R30">
-        <v>98.49708300600477</v>
+        <v>92.65151927396002</v>
       </c>
       <c r="S30">
         <v>22.14109992980957</v>
       </c>
       <c r="T30">
-        <v>76.3559830761952</v>
+        <v>70.51041934415045</v>
       </c>
       <c r="U30">
         <v>0.525</v>
@@ -4211,7 +4211,7 @@
         <v>1</v>
       </c>
       <c r="X30">
-        <v>11.7370808697743</v>
+        <v>5.891517137729556</v>
       </c>
       <c r="Y30">
         <v>98.11846750906066</v>
@@ -4309,13 +4309,13 @@
         <v>0</v>
       </c>
       <c r="R31">
-        <v>94.8370793438954</v>
+        <v>88.99151561185064</v>
       </c>
       <c r="S31">
         <v>30.96780395507812</v>
       </c>
       <c r="T31">
-        <v>63.86927538881727</v>
+        <v>58.02371165677252</v>
       </c>
       <c r="U31">
         <v>0.525</v>
@@ -4327,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="X31">
-        <v>11.7370808697743</v>
+        <v>5.891517137729556</v>
       </c>
       <c r="Y31">
         <v>103.4584638469513</v>
@@ -4425,13 +4425,13 @@
         <v>20.8453540802002</v>
       </c>
       <c r="R32">
-        <v>92.76707964907118</v>
+        <v>86.92151591702643</v>
       </c>
       <c r="S32">
         <v>41.9760627746582</v>
       </c>
       <c r="T32">
-        <v>50.79101687441297</v>
+        <v>44.94545314236822</v>
       </c>
       <c r="U32">
         <v>0.525</v>
@@ -4443,7 +4443,7 @@
         <v>1</v>
       </c>
       <c r="X32">
-        <v>11.7370808697743</v>
+        <v>5.891517137729556</v>
       </c>
       <c r="Y32">
         <v>101.3884641521271</v>
@@ -4541,13 +4541,13 @@
         <v>21.41829957167307</v>
       </c>
       <c r="R33">
-        <v>94.74062248332096</v>
+        <v>91.18067037959381</v>
       </c>
       <c r="S33">
         <v>51.7120246887207</v>
       </c>
       <c r="T33">
-        <v>43.02859779460026</v>
+        <v>39.4686456908731</v>
       </c>
       <c r="U33">
         <v>0.525</v>
@@ -4559,7 +4559,7 @@
         <v>1</v>
       </c>
       <c r="X33">
-        <v>12.69061943156315</v>
+        <v>9.130667327835996</v>
       </c>
       <c r="Y33">
         <v>103.6001653516629</v>
@@ -4657,13 +4657,13 @@
         <v>21.68934801135613</v>
       </c>
       <c r="R34">
-        <v>102.3727487400851</v>
+        <v>100.7208838656748</v>
       </c>
       <c r="S34">
         <v>63.06760787963867</v>
       </c>
       <c r="T34">
-        <v>39.30514086044646</v>
+        <v>37.65327598603614</v>
       </c>
       <c r="U34">
         <v>0.525</v>
@@ -4675,7 +4675,7 @@
         <v>1</v>
       </c>
       <c r="X34">
-        <v>14.0295322866426</v>
+        <v>12.37766741223228</v>
       </c>
       <c r="Y34">
         <v>109.8101644361355</v>
@@ -4773,13 +4773,13 @@
         <v>21.80822476750285</v>
       </c>
       <c r="R35">
-        <v>131.5060323347459</v>
+        <v>131.408844760721</v>
       </c>
       <c r="S35">
         <v>77.47518920898438</v>
       </c>
       <c r="T35">
-        <v>54.03084312576152</v>
+        <v>53.93365555173659</v>
       </c>
       <c r="U35">
         <v>0.525</v>
@@ -4791,7 +4791,7 @@
         <v>1</v>
       </c>
       <c r="X35">
-        <v>15.76879074474119</v>
+        <v>15.67160317071624</v>
       </c>
       <c r="Y35">
         <v>147.9601659620144</v>
@@ -4889,13 +4889,13 @@
         <v>21.85015697775894</v>
       </c>
       <c r="R36">
-        <v>139.3752308761858</v>
+        <v>139.2780433021609</v>
       </c>
       <c r="S36">
         <v>87.20231628417969</v>
       </c>
       <c r="T36">
-        <v>52.17291459200615</v>
+        <v>52.07572701798119</v>
       </c>
       <c r="U36">
         <v>0.525</v>
@@ -4907,7 +4907,7 @@
         <v>1</v>
       </c>
       <c r="X36">
-        <v>15.76879074474119</v>
+        <v>15.67160317071624</v>
       </c>
       <c r="Y36">
         <v>150.450163825784</v>
@@ -5005,13 +5005,13 @@
         <v>21.86552180746851</v>
       </c>
       <c r="R37">
-        <v>144.4275894199971</v>
+        <v>144.3304018459721</v>
       </c>
       <c r="S37">
         <v>98.79735565185547</v>
       </c>
       <c r="T37">
-        <v>45.63023376814161</v>
+        <v>45.53304619411668</v>
       </c>
       <c r="U37">
         <v>0.525</v>
@@ -5023,7 +5023,7 @@
         <v>1</v>
       </c>
       <c r="X37">
-        <v>15.76879074474119</v>
+        <v>15.67160317071624</v>
       </c>
       <c r="Y37">
         <v>159.9130098326686</v>
@@ -5121,13 +5121,13 @@
         <v>22.05547065191401</v>
       </c>
       <c r="R38">
-        <v>120.2537264524269</v>
+        <v>120.1565388784019</v>
       </c>
       <c r="S38">
         <v>109.1441040039062</v>
       </c>
       <c r="T38">
-        <v>11.10962244852062</v>
+        <v>11.01243487449568</v>
       </c>
       <c r="U38">
         <v>0.525</v>
@@ -5139,7 +5139,7 @@
         <v>1</v>
       </c>
       <c r="X38">
-        <v>15.76879074474119</v>
+        <v>15.67160317071624</v>
       </c>
       <c r="Y38">
         <v>130.6330186827663</v>
@@ -5237,13 +5237,13 @@
         <v>22.30989066173849</v>
       </c>
       <c r="R39">
-        <v>132.8721667613206</v>
+        <v>132.9115766104075</v>
       </c>
       <c r="S39">
         <v>118.8153686523438</v>
       </c>
       <c r="T39">
-        <v>14.05679810897684</v>
+        <v>14.09620795806376</v>
       </c>
       <c r="U39">
         <v>0.525</v>
@@ -5255,7 +5255,7 @@
         <v>1</v>
       </c>
       <c r="X39">
-        <v>18.49787268748607</v>
+        <v>18.53728253657299</v>
       </c>
       <c r="Y39">
         <v>129.0530168517116</v>
@@ -5353,13 +5353,13 @@
         <v>22.58327471205234</v>
       </c>
       <c r="R40">
-        <v>138.0074317176137</v>
+        <v>138.0468415667007</v>
       </c>
       <c r="S40">
         <v>128.3525848388672</v>
       </c>
       <c r="T40">
-        <v>9.654846878746554</v>
+        <v>9.694256727833476</v>
       </c>
       <c r="U40">
         <v>0.525</v>
@@ -5371,7 +5371,7 @@
         <v>1</v>
       </c>
       <c r="X40">
-        <v>18.49787268748607</v>
+        <v>18.53728253657299</v>
       </c>
       <c r="Y40">
         <v>129.7430192931178</v>
@@ -5469,7 +5469,7 @@
         <v>22.86249613533688</v>
       </c>
       <c r="R41">
-        <v>133.991803811625</v>
+        <v>134.1893445111257</v>
       </c>
       <c r="S41">
         <v>137.5313873291016</v>
@@ -5484,10 +5484,10 @@
         <v>0.55</v>
       </c>
       <c r="W41">
-        <v>0.9742634493389741</v>
+        <v>0.9756997810981238</v>
       </c>
       <c r="X41">
-        <v>20.63228532975769</v>
+        <v>20.82982602925839</v>
       </c>
       <c r="Y41">
         <v>122.8730165465358</v>
@@ -5585,7 +5585,7 @@
         <v>23.13660696126185</v>
       </c>
       <c r="R42">
-        <v>132.601203771129</v>
+        <v>132.7987444706297</v>
       </c>
       <c r="S42">
         <v>144.0757751464844</v>
@@ -5600,10 +5600,10 @@
         <v>0.55</v>
       </c>
       <c r="W42">
-        <v>0.9203573858014023</v>
+        <v>0.921728474725268</v>
       </c>
       <c r="X42">
-        <v>20.63228532975769</v>
+        <v>20.82982602925839</v>
       </c>
       <c r="Y42">
         <v>121.3730165465358</v>
@@ -5701,7 +5701,7 @@
         <v>23.36085164874881</v>
       </c>
       <c r="R43">
-        <v>143.4552424939091</v>
+        <v>143.6527831934098</v>
       </c>
       <c r="S43">
         <v>150.8756713867188</v>
@@ -5716,10 +5716,10 @@
         <v>0.55</v>
       </c>
       <c r="W43">
-        <v>0.9508175915665692</v>
+        <v>0.9521268861512102</v>
       </c>
       <c r="X43">
-        <v>20.63228532975769</v>
+        <v>20.82982602925839</v>
       </c>
       <c r="Y43">
         <v>131.6030199034694</v>
@@ -5817,13 +5817,13 @@
         <v>23.56293896571148</v>
       </c>
       <c r="R44">
-        <v>161.4872820204833</v>
+        <v>161.684822719984</v>
       </c>
       <c r="S44">
         <v>155.5123138427734</v>
       </c>
       <c r="T44">
-        <v>5.974968177709826</v>
+        <v>6.172508877210532</v>
       </c>
       <c r="U44">
         <v>0.525</v>
@@ -5835,7 +5835,7 @@
         <v>1</v>
       </c>
       <c r="X44">
-        <v>20.63228532975769</v>
+        <v>20.82982602925839</v>
       </c>
       <c r="Y44">
         <v>148.9753896946735</v>
@@ -5933,7 +5933,7 @@
         <v>23.71447340882256</v>
       </c>
       <c r="R45">
-        <v>148.2447125252586</v>
+        <v>148.4422532247593</v>
       </c>
       <c r="S45">
         <v>159.5862121582031</v>
@@ -5948,10 +5948,10 @@
         <v>0.55</v>
       </c>
       <c r="W45">
-        <v>0.9289318326466617</v>
+        <v>0.9301696632639136</v>
       </c>
       <c r="X45">
-        <v>20.63228532975769</v>
+        <v>20.82982602925839</v>
       </c>
       <c r="Y45">
         <v>143.8756843487747</v>
@@ -6049,7 +6049,7 @@
         <v>23.82960851524932</v>
       </c>
       <c r="R46">
-        <v>144.4026306476108</v>
+        <v>144.9052109223654</v>
       </c>
       <c r="S46">
         <v>163.8546295166016</v>
@@ -6064,10 +6064,10 @@
         <v>0.55</v>
       </c>
       <c r="W46">
-        <v>0.8812850212021632</v>
+        <v>0.8843522538841895</v>
       </c>
       <c r="X46">
-        <v>22.16128054865208</v>
+        <v>22.66386082340671</v>
       </c>
       <c r="Y46">
         <v>140.3580657563741</v>
@@ -6165,13 +6165,13 @@
         <v>23.92811613687611</v>
       </c>
       <c r="R47">
-        <v>169.8501641789624</v>
+        <v>170.352744453717</v>
       </c>
       <c r="S47">
         <v>167.7201843261719</v>
       </c>
       <c r="T47">
-        <v>2.129979852790541</v>
+        <v>2.632560127545162</v>
       </c>
       <c r="U47">
         <v>0.525</v>
@@ -6183,7 +6183,7 @@
         <v>1</v>
       </c>
       <c r="X47">
-        <v>22.16128054865208</v>
+        <v>22.66386082340671</v>
       </c>
       <c r="Y47">
         <v>165.1923205637448</v>
@@ -6281,7 +6281,7 @@
         <v>24.00972311281093</v>
       </c>
       <c r="R48">
-        <v>167.2964043907421</v>
+        <v>167.7989846654968</v>
       </c>
       <c r="S48">
         <v>170.2121429443359</v>
@@ -6296,10 +6296,10 @@
         <v>0.425</v>
       </c>
       <c r="W48">
-        <v>0.9828699732982779</v>
+        <v>0.9858226432198298</v>
       </c>
       <c r="X48">
-        <v>22.16128054865208</v>
+        <v>22.66386082340671</v>
       </c>
       <c r="Y48">
         <v>163.2076158482369</v>
@@ -6397,13 +6397,13 @@
         <v>24.05750476560548</v>
       </c>
       <c r="R49">
-        <v>170.1772681178342</v>
+        <v>171.066488282285</v>
       </c>
       <c r="S49">
         <v>170.7550659179688</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>0.3114223643162575</v>
       </c>
       <c r="U49">
         <v>0.525</v>
@@ -6412,10 +6412,10 @@
         <v>0.425</v>
       </c>
       <c r="W49">
-        <v>0.9966162186929661</v>
+        <v>1</v>
       </c>
       <c r="X49">
-        <v>23.24186849427453</v>
+        <v>24.13108865872537</v>
       </c>
       <c r="Y49">
         <v>165.189267322236</v>
@@ -6513,7 +6513,7 @@
         <v>24.05284149739113</v>
       </c>
       <c r="R50">
-        <v>167.8179364672477</v>
+        <v>168.7071566316986</v>
       </c>
       <c r="S50">
         <v>172.9508666992188</v>
@@ -6528,10 +6528,10 @@
         <v>0.425</v>
       </c>
       <c r="W50">
-        <v>0.9703214541220091</v>
+        <v>0.9754629152862213</v>
       </c>
       <c r="X50">
-        <v>23.24186849427453</v>
+        <v>24.13108865872537</v>
       </c>
       <c r="Y50">
         <v>161.3721831402596</v>
@@ -6629,7 +6629,7 @@
         <v>24.04922077223083</v>
       </c>
       <c r="R51">
-        <v>166.6954921113513</v>
+        <v>168.0080045893717</v>
       </c>
       <c r="S51">
         <v>172.7935638427734</v>
@@ -6644,10 +6644,10 @@
         <v>0.425</v>
       </c>
       <c r="W51">
-        <v>0.9647089185742422</v>
+        <v>0.9723047598129512</v>
       </c>
       <c r="X51">
-        <v>23.99235844895991</v>
+        <v>25.3048709269803</v>
       </c>
       <c r="Y51">
         <v>160.4554019143214</v>
@@ -6745,7 +6745,7 @@
         <v>24.00336526051504</v>
       </c>
       <c r="R52">
-        <v>163.0982511697235</v>
+        <v>164.4107636477439</v>
       </c>
       <c r="S52">
         <v>172.4795379638672</v>
@@ -6760,10 +6760,10 @@
         <v>0.425</v>
       </c>
       <c r="W52">
-        <v>0.9456092768748662</v>
+        <v>0.9532189475263225</v>
       </c>
       <c r="X52">
-        <v>23.99235844895991</v>
+        <v>25.3048709269803</v>
       </c>
       <c r="Y52">
         <v>154.9626291648021</v>
@@ -6861,7 +6861,7 @@
         <v>23.93230251078641</v>
       </c>
       <c r="R53">
-        <v>158.8386037937207</v>
+        <v>160.1511162717411</v>
       </c>
       <c r="S53">
         <v>169.0163726806641</v>
@@ -6876,10 +6876,10 @@
         <v>0.425</v>
       </c>
       <c r="W53">
-        <v>0.9397823493338542</v>
+        <v>0.9475479430287338</v>
       </c>
       <c r="X53">
-        <v>23.99235844895991</v>
+        <v>25.3048709269803</v>
       </c>
       <c r="Y53">
         <v>151.1759452661147</v>
@@ -6977,7 +6977,7 @@
         <v>23.79211708769699</v>
       </c>
       <c r="R54">
-        <v>157.9509449425564</v>
+        <v>159.2634574205768</v>
       </c>
       <c r="S54">
         <v>165.8521270751953</v>
@@ -6992,10 +6992,10 @@
         <v>0.425</v>
       </c>
       <c r="W54">
-        <v>0.9523600795963465</v>
+        <v>0.9602738308467318</v>
       </c>
       <c r="X54">
-        <v>23.99235844895991</v>
+        <v>25.3048709269803</v>
       </c>
       <c r="Y54">
         <v>149.7980944421897</v>
@@ -7093,13 +7093,13 @@
         <v>23.62133981717089</v>
       </c>
       <c r="R55">
-        <v>169.6998500199306</v>
+        <v>171.6236879884659</v>
       </c>
       <c r="S55">
         <v>162.6152801513672</v>
       </c>
       <c r="T55">
-        <v>7.084569868563449</v>
+        <v>9.008407837098702</v>
       </c>
       <c r="U55">
         <v>0.525</v>
@@ -7111,7 +7111,7 @@
         <v>1</v>
       </c>
       <c r="X55">
-        <v>24.32005877304897</v>
+        <v>26.24389674158424</v>
       </c>
       <c r="Y55">
         <v>161.7272595332662</v>
@@ -7209,13 +7209,13 @@
         <v>23.43250838896954</v>
       </c>
       <c r="R56">
-        <v>178.1781715539326</v>
+        <v>180.6686940948967</v>
       </c>
       <c r="S56">
         <v>158.8567962646484</v>
       </c>
       <c r="T56">
-        <v>19.32137528928416</v>
+        <v>21.81189783024828</v>
       </c>
       <c r="U56">
         <v>0.525</v>
@@ -7227,7 +7227,7 @@
         <v>1</v>
       </c>
       <c r="X56">
-        <v>24.50459485230326</v>
+        <v>26.99511739326739</v>
       </c>
       <c r="Y56">
         <v>170.9022698512408</v>
@@ -7325,13 +7325,13 @@
         <v>23.2239964192491</v>
       </c>
       <c r="R57">
-        <v>156.8706328014229</v>
+        <v>159.361155342387</v>
       </c>
       <c r="S57">
         <v>152.260498046875</v>
       </c>
       <c r="T57">
-        <v>4.610134754547886</v>
+        <v>7.100657295512008</v>
       </c>
       <c r="U57">
         <v>0.525</v>
@@ -7343,7 +7343,7 @@
         <v>1</v>
       </c>
       <c r="X57">
-        <v>24.50459485230326</v>
+        <v>26.99511739326739</v>
       </c>
       <c r="Y57">
         <v>150.4723577761799</v>
@@ -7441,13 +7441,13 @@
         <v>22.95517626422475</v>
       </c>
       <c r="R58">
-        <v>144.420454455083</v>
+        <v>147.4896946755013</v>
       </c>
       <c r="S58">
         <v>146.9972534179688</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>0.4924412575325903</v>
       </c>
       <c r="U58">
         <v>0.525</v>
@@ -7456,10 +7456,10 @@
         <v>0.425</v>
       </c>
       <c r="W58">
-        <v>0.982470427827934</v>
+        <v>1</v>
       </c>
       <c r="X58">
-        <v>24.48381536758004</v>
+        <v>27.5530555879984</v>
       </c>
       <c r="Y58">
         <v>138.5008828629384</v>
@@ -7557,13 +7557,13 @@
         <v>22.67771840841979</v>
       </c>
       <c r="R59">
-        <v>154.4566533177929</v>
+        <v>157.5258935382112</v>
       </c>
       <c r="S59">
         <v>140.6554718017578</v>
       </c>
       <c r="T59">
-        <v>13.80118151603506</v>
+        <v>16.87042173645344</v>
       </c>
       <c r="U59">
         <v>0.525</v>
@@ -7575,7 +7575,7 @@
         <v>1</v>
       </c>
       <c r="X59">
-        <v>24.48381536758004</v>
+        <v>27.5530555879984</v>
       </c>
       <c r="Y59">
         <v>148.1124921510025</v>
@@ -7673,13 +7673,13 @@
         <v>22.37595109124998</v>
       </c>
       <c r="R60">
-        <v>141.4266386641222</v>
+        <v>144.9825952918764</v>
       </c>
       <c r="S60">
         <v>131.0868225097656</v>
       </c>
       <c r="T60">
-        <v>10.33981615435655</v>
+        <v>13.89577278211078</v>
       </c>
       <c r="U60">
         <v>0.525</v>
@@ -7691,7 +7691,7 @@
         <v>1</v>
       </c>
       <c r="X60">
-        <v>24.28172390350512</v>
+        <v>27.83768053125934</v>
       </c>
       <c r="Y60">
         <v>135.5320348770869</v>
@@ -7789,13 +7789,13 @@
         <v>22.0047117114308</v>
       </c>
       <c r="R61">
-        <v>150.6234911085851</v>
+        <v>154.1794477363393</v>
       </c>
       <c r="S61">
         <v>125.5129318237305</v>
       </c>
       <c r="T61">
-        <v>25.11055928485465</v>
+        <v>28.66651591260887</v>
       </c>
       <c r="U61">
         <v>0.525</v>
@@ -7807,7 +7807,7 @@
         <v>1</v>
       </c>
       <c r="X61">
-        <v>24.28172390350512</v>
+        <v>27.83768053125934</v>
       </c>
       <c r="Y61">
         <v>144.889740166742</v>
@@ -7905,13 +7905,13 @@
         <v>21.6667167822644</v>
       </c>
       <c r="R62">
-        <v>144.4439451211921</v>
+        <v>147.9999017489463</v>
       </c>
       <c r="S62">
         <v>115.4699401855469</v>
       </c>
       <c r="T62">
-        <v>28.97400493564521</v>
+        <v>32.52996156339941</v>
       </c>
       <c r="U62">
         <v>0.525</v>
@@ -7923,7 +7923,7 @@
         <v>1</v>
       </c>
       <c r="X62">
-        <v>24.28172390350512</v>
+        <v>27.83768053125934</v>
       </c>
       <c r="Y62">
         <v>138.8147485287239</v>
@@ -8021,13 +8021,13 @@
         <v>21.26653465622653</v>
       </c>
       <c r="R63">
-        <v>146.0225398521786</v>
+        <v>149.5784964799328</v>
       </c>
       <c r="S63">
         <v>104.1723861694336</v>
       </c>
       <c r="T63">
-        <v>41.85015368274503</v>
+        <v>45.40611031049923</v>
       </c>
       <c r="U63">
         <v>0.525</v>
@@ -8039,7 +8039,7 @@
         <v>1</v>
       </c>
       <c r="X63">
-        <v>24.28172390350512</v>
+        <v>27.83768053125934</v>
       </c>
       <c r="Y63">
         <v>140.5524972654037</v>
@@ -8137,13 +8137,13 @@
         <v>20.81201045824857</v>
       </c>
       <c r="R64">
-        <v>139.9557487535914</v>
+        <v>143.9455782930279</v>
       </c>
       <c r="S64">
         <v>95.44938659667969</v>
       </c>
       <c r="T64">
-        <v>44.50636215691173</v>
+        <v>48.49619169634821</v>
       </c>
       <c r="U64">
         <v>0.525</v>
@@ -8155,7 +8155,7 @@
         <v>1</v>
       </c>
       <c r="X64">
-        <v>23.69014522695834</v>
+        <v>27.67997476639481</v>
       </c>
       <c r="Y64">
         <v>135.0895412684643</v>
@@ -8253,13 +8253,13 @@
         <v>20.37416212170918</v>
       </c>
       <c r="R65">
-        <v>125.6047584952289</v>
+        <v>129.5945880346654</v>
       </c>
       <c r="S65">
         <v>90.14130401611328</v>
       </c>
       <c r="T65">
-        <v>35.46345447911564</v>
+        <v>39.4532840185521</v>
       </c>
       <c r="U65">
         <v>0.525</v>
@@ -8271,7 +8271,7 @@
         <v>1</v>
       </c>
       <c r="X65">
-        <v>23.69014522695834</v>
+        <v>27.67997476639481</v>
       </c>
       <c r="Y65">
         <v>137.7066195195015</v>
@@ -8369,13 +8369,13 @@
         <v>20.00240651016253</v>
       </c>
       <c r="R66">
-        <v>112.7570179390007</v>
+        <v>117.1149820701676</v>
       </c>
       <c r="S66">
         <v>85.19937133789062</v>
       </c>
       <c r="T66">
-        <v>27.55764660111008</v>
+        <v>31.91561073227695</v>
       </c>
       <c r="U66">
         <v>0.525</v>
@@ -8387,7 +8387,7 @@
         <v>1</v>
       </c>
       <c r="X66">
-        <v>22.97001786503986</v>
+        <v>27.32798199620673</v>
       </c>
       <c r="Y66">
         <v>125.344388982901</v>
@@ -8485,13 +8485,13 @@
         <v>19.69061292489675</v>
       </c>
       <c r="R67">
-        <v>132.0705632744425</v>
+        <v>136.4285274056094</v>
       </c>
       <c r="S67">
         <v>67.21014404296875</v>
       </c>
       <c r="T67">
-        <v>64.86041923147377</v>
+        <v>69.21838336264065</v>
       </c>
       <c r="U67">
         <v>0.525</v>
@@ -8503,7 +8503,7 @@
         <v>1</v>
       </c>
       <c r="X67">
-        <v>22.97001786503986</v>
+        <v>27.32798199620673</v>
       </c>
       <c r="Y67">
         <v>132.1980744515845</v>
@@ -8601,13 +8601,13 @@
         <v>19.46999201639155</v>
       </c>
       <c r="R68">
-        <v>140.9783955130731</v>
+        <v>145.33635964424</v>
       </c>
       <c r="S68">
         <v>52.87920761108398</v>
       </c>
       <c r="T68">
-        <v>88.0991879019891</v>
+        <v>92.45715203315598</v>
       </c>
       <c r="U68">
         <v>0.525</v>
@@ -8619,7 +8619,7 @@
         <v>1</v>
       </c>
       <c r="X68">
-        <v>22.97001786503986</v>
+        <v>27.32798199620673</v>
       </c>
       <c r="Y68">
         <v>123.4589495980675</v>
@@ -8717,13 +8717,13 @@
         <v>19.29192946050811</v>
       </c>
       <c r="R69">
-        <v>138.9910186019286</v>
+        <v>143.3489827330955</v>
       </c>
       <c r="S69">
         <v>41.07754898071289</v>
       </c>
       <c r="T69">
-        <v>97.91346962121571</v>
+        <v>102.2714337523826</v>
       </c>
       <c r="U69">
         <v>0.525</v>
@@ -8735,7 +8735,7 @@
         <v>1</v>
       </c>
       <c r="X69">
-        <v>22.97001786503986</v>
+        <v>27.32798199620673</v>
       </c>
       <c r="Y69">
         <v>121.5324791880138</v>
@@ -8833,13 +8833,13 @@
         <v>19.13154803762582</v>
       </c>
       <c r="R70">
-        <v>124.7357040814368</v>
+        <v>148.5468017556441</v>
       </c>
       <c r="S70">
         <v>30.0517578125</v>
       </c>
       <c r="T70">
-        <v>94.68394626893682</v>
+        <v>118.4950439431441</v>
       </c>
       <c r="U70">
         <v>0.525</v>
@@ -8851,7 +8851,7 @@
         <v>1</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>23.81109767420725</v>
       </c>
       <c r="Y70">
         <v>107.1779482930238</v>
@@ -8949,13 +8949,13 @@
         <v>18.16444643233461</v>
       </c>
       <c r="R71">
-        <v>126.0106593145557</v>
+        <v>149.8217569887629</v>
       </c>
       <c r="S71">
         <v>20.7983455657959</v>
       </c>
       <c r="T71">
-        <v>105.2123137487598</v>
+        <v>129.023411422967</v>
       </c>
       <c r="U71">
         <v>0.525</v>
@@ -8967,7 +8967,7 @@
         <v>1</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>23.81109767420725</v>
       </c>
       <c r="Y71">
         <v>118.9846651087272</v>
@@ -9065,13 +9065,13 @@
         <v>18.16444643233461</v>
       </c>
       <c r="R72">
-        <v>155.9491938998718</v>
+        <v>179.7602915740791</v>
       </c>
       <c r="S72">
         <v>13.46586036682129</v>
       </c>
       <c r="T72">
-        <v>142.4833335330505</v>
+        <v>166.2944312072578</v>
       </c>
       <c r="U72">
         <v>0.525</v>
@@ -9083,7 +9083,7 @@
         <v>1</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>23.81109767420725</v>
       </c>
       <c r="Y72">
         <v>148.5415353113953</v>
@@ -9181,13 +9181,13 @@
         <v>18.16444643233461</v>
       </c>
       <c r="R73">
-        <v>178.1532295921995</v>
+        <v>197.8222241869695</v>
       </c>
       <c r="S73">
         <v>6.369131565093994</v>
       </c>
       <c r="T73">
-        <v>171.7840980271055</v>
+        <v>191.4530926218755</v>
       </c>
       <c r="U73">
         <v>0.525</v>
@@ -9199,7 +9199,7 @@
         <v>0.2738263010978699</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>19.66899459477</v>
       </c>
       <c r="Y73">
         <v>170.7654951142722</v>
@@ -9297,13 +9297,13 @@
         <v>18.16444643233461</v>
       </c>
       <c r="R74">
-        <v>170.8058639311286</v>
+        <v>190.4748585258985</v>
       </c>
       <c r="S74">
         <v>2.990052223205566</v>
       </c>
       <c r="T74">
-        <v>167.815811707923</v>
+        <v>187.484806302693</v>
       </c>
       <c r="U74">
         <v>0.525</v>
@@ -9315,7 +9315,7 @@
         <v>0</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>19.66899459477</v>
       </c>
       <c r="Y74">
         <v>163.4310801250582</v>
@@ -9413,13 +9413,13 @@
         <v>18.16444643233461</v>
       </c>
       <c r="R75">
-        <v>192.22756846945</v>
+        <v>208.3067403953744</v>
       </c>
       <c r="S75">
         <v>0.8573274612426758</v>
       </c>
       <c r="T75">
-        <v>191.3702410082073</v>
+        <v>207.4494129341317</v>
       </c>
       <c r="U75">
         <v>0.525</v>
@@ -9431,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>16.07917192592438</v>
       </c>
       <c r="Y75">
         <v>184.8612026000866</v>
@@ -9529,13 +9529,13 @@
         <v>18.16444643233461</v>
       </c>
       <c r="R76">
-        <v>193.9986666232163</v>
+        <v>207.081117016887</v>
       </c>
       <c r="S76">
         <v>1.143430590629578</v>
       </c>
       <c r="T76">
-        <v>192.8552360325868</v>
+        <v>205.9376864262574</v>
       </c>
       <c r="U76">
         <v>0.525</v>
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>13.08245039367065</v>
       </c>
       <c r="Y76">
         <v>175.6377724127126</v>
@@ -9645,16 +9645,16 @@
         <v>18.16444643233461</v>
       </c>
       <c r="R77">
-        <v>178.8793924470903</v>
+        <v>189.455493922876</v>
       </c>
       <c r="S77">
         <v>1.037100076675415</v>
       </c>
       <c r="T77">
-        <v>177.8422923704148</v>
+        <v>188.4183938462006</v>
       </c>
       <c r="U77">
-        <v>0.507850816911804</v>
+        <v>0.5051756869128678</v>
       </c>
       <c r="V77">
         <v>0.55</v>
@@ -9663,7 +9663,7 @@
         <v>0</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>10.57610147578571</v>
       </c>
       <c r="Y77">
         <v>160.5220548148452</v>
@@ -9761,16 +9761,16 @@
         <v>18.16444643233461</v>
       </c>
       <c r="R78">
-        <v>208.4998561759677</v>
+        <v>219.0759576517534</v>
       </c>
       <c r="S78">
         <v>0.6469324231147766</v>
       </c>
       <c r="T78">
-        <v>207.8529237528529</v>
+        <v>218.4290252286386</v>
       </c>
       <c r="U78">
-        <v>0.507850816911804</v>
+        <v>0.4864827953962031</v>
       </c>
       <c r="V78">
         <v>0.55</v>
@@ -9779,7 +9779,7 @@
         <v>0</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>10.57610147578571</v>
       </c>
       <c r="Y78">
         <v>186.1448303195908</v>
@@ -9886,7 +9886,7 @@
         <v>170.0690751274136</v>
       </c>
       <c r="U79">
-        <v>0.487257111603833</v>
+        <v>0.463726464167376</v>
       </c>
       <c r="V79">
         <v>0.55</v>
@@ -10002,7 +10002,7 @@
         <v>184.7664675431044</v>
       </c>
       <c r="U80">
-        <v>0.4679389163514951</v>
+        <v>0.4444082689150381</v>
       </c>
       <c r="V80">
         <v>0.55</v>
@@ -10118,7 +10118,7 @@
         <v>191.5443734156654</v>
       </c>
       <c r="U81">
-        <v>0.4453120383297903</v>
+        <v>0.4217813908933332</v>
       </c>
       <c r="V81">
         <v>0.55</v>
@@ -10234,7 +10234,7 @@
         <v>191.5050772856143</v>
       </c>
       <c r="U82">
-        <v>0.4226610513888364</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V82">
         <v>0.55</v>
@@ -10350,7 +10350,7 @@
         <v>179.1909892633785</v>
       </c>
       <c r="U83">
-        <v>0.4009075960957646</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V83">
         <v>0.55</v>
@@ -10466,7 +10466,7 @@
         <v>195.5112148452499</v>
       </c>
       <c r="U84">
-        <v>0.3791508898300658</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V84">
         <v>0.55</v>
@@ -10582,7 +10582,7 @@
         <v>175.9377459087974</v>
       </c>
       <c r="U85">
-        <v>0.3791508898300658</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V85">
         <v>0.55</v>
@@ -10698,7 +10698,7 @@
         <v>186.7110739546412</v>
       </c>
       <c r="U86">
-        <v>0.3791508898300658</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V86">
         <v>0.55</v>
@@ -10814,7 +10814,7 @@
         <v>193.8863890198515</v>
       </c>
       <c r="U87">
-        <v>0.3791508898300658</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V87">
         <v>0.55</v>
@@ -10930,7 +10930,7 @@
         <v>187.1367207240588</v>
       </c>
       <c r="U88">
-        <v>0.3791508898300658</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V88">
         <v>0.55</v>
@@ -11046,7 +11046,7 @@
         <v>172.5535398011743</v>
       </c>
       <c r="U89">
-        <v>0.3791508898300658</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V89">
         <v>0.55</v>
@@ -11162,7 +11162,7 @@
         <v>190.8583633890243</v>
       </c>
       <c r="U90">
-        <v>0.3791508898300658</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V90">
         <v>0.55</v>
@@ -11278,7 +11278,7 @@
         <v>181.4131046785793</v>
       </c>
       <c r="U91">
-        <v>0.3791508898300658</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V91">
         <v>0.425</v>
@@ -11394,7 +11394,7 @@
         <v>149.6956395202531</v>
       </c>
       <c r="U92">
-        <v>0.3791508898300658</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V92">
         <v>0.425</v>
@@ -11510,7 +11510,7 @@
         <v>165.2792547161653</v>
       </c>
       <c r="U93">
-        <v>0.3791508898300658</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V93">
         <v>0.425</v>
@@ -11626,7 +11626,7 @@
         <v>135.3903300361787</v>
       </c>
       <c r="U94">
-        <v>0.3791508898300658</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V94">
         <v>0.425</v>
@@ -11742,7 +11742,7 @@
         <v>150.8726779456472</v>
       </c>
       <c r="U95">
-        <v>0.3791508898300658</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V95">
         <v>0.3</v>
@@ -11858,7 +11858,7 @@
         <v>110.4463833268914</v>
       </c>
       <c r="U96">
-        <v>0.3791508898300658</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V96">
         <v>0.3</v>
@@ -11974,7 +11974,7 @@
         <v>116.3778245665505</v>
       </c>
       <c r="U97">
-        <v>0.3791508898300658</v>
+        <v>0.3991304039523793</v>
       </c>
       <c r="V97">
         <v>0.3</v>
